--- a/dist/Otchet/2026-03-30.xlsx
+++ b/dist/Otchet/2026-03-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Время</t>
   </si>
@@ -38,6 +38,15 @@
   </si>
   <si>
     <t>22:46:51</t>
+  </si>
+  <si>
+    <t>22:53:16</t>
+  </si>
+  <si>
+    <t>Бебро</t>
+  </si>
+  <si>
+    <t>909</t>
   </si>
 </sst>
 </file>
@@ -401,6 +410,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>